--- a/southern_europe/italy_data/geographical_feature/node_metrics.xlsx
+++ b/southern_europe/italy_data/geographical_feature/node_metrics.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE28086-DB60-416D-946A-C96FF42EC5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nodes" sheetId="1" r:id="rId1"/>
@@ -689,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -714,8 +714,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2146,10 +2145,10 @@
       <c r="B47" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="C47" s="24">
+      <c r="C47" s="4">
         <v>11.579599999999999</v>
       </c>
-      <c r="D47" s="25">
+      <c r="D47" s="24">
         <v>44.861989999999999</v>
       </c>
       <c r="E47" s="4">
